--- a/ZlaataQA/reports/Automation_Report.xlsx
+++ b/ZlaataQA/reports/Automation_Report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV23\ZlaataQA\reports\"/>
     </mc:Choice>
@@ -15,13 +15,20 @@
   <sheets>
     <sheet name="2026-06-20" sheetId="43" r:id="rId1"/>
     <sheet name="2026-07-02" sheetId="44" r:id="rId2"/>
+    <sheet name="2026-07-06" r:id="rId6" sheetId="45"/>
+    <sheet name="2026-07-07" r:id="rId7" sheetId="46"/>
+    <sheet name="2026-07-08" r:id="rId8" sheetId="47"/>
+    <sheet name="2026-07-09" r:id="rId9" sheetId="48"/>
+    <sheet name="2026-07-10" r:id="rId10" sheetId="49"/>
+    <sheet name="2026-07-14" r:id="rId11" sheetId="50"/>
+    <sheet name="2026-07-20" r:id="rId12" sheetId="51"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="97">
   <si>
     <t>TestCase Name</t>
   </si>
@@ -114,13 +121,212 @@
   </si>
   <si>
     <t>TC_UI_Zlaata_Raw_01 |Verify admin can add a new raw material successfully.|"TD_UI_Zlaata_Raw_01"</t>
+  </si>
+  <si>
+    <t>TestCase ID</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 67 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ProductStock_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ProductStock_01 |Verify that stock changes are reflected and saved successfully after adding stock.| "TD_UI_Zlaata_ProductStock_01"</t>
+  </si>
+  <si>
+    <t>FEATURE FILES: ProductStock</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 0 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 44 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 46 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PS_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PS_01 |Verify that stock changes are reflected and saved successfully after adding stock.| "TD_UI_Zlaata_PS_01"</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 92 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PS_01 |Verify that stock changes are reflected and saved successfully after adjusting stock.| "TD_UI_Zlaata_PS_01"</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 81 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 127 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 87 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 104 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 113 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 178 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 160 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 144 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 164 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 165 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 263 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 192 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 124 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 125 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 90 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 115 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 107 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 153 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PS_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PS_02 |Verify that stock changes are reflected and saved successfully after adding stock.| "TD_UI_Zlaata_PS_02"</t>
+  </si>
+  <si>
+    <t>TOTAL TEST CASE EXECUTED : 0</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 173 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 180 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 119 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 213 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 51 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 134 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 143 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 114 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 133 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 103 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 226 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 261 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TEST CASE EXECUTED : 2</t>
+  </si>
+  <si>
+    <t>TOTAL PASSED : 2</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 337 sec</t>
+  </si>
+  <si>
+    <t>FEATURES RUNNED: 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEATURE FILES: </t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 152 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PS_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PS_03 |Verify that the low stock alert is saved and reflected successfully for the product.| "TD_UI_Zlaata_PS_03"</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 236 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 221 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 259 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 274 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 248 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 267 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TEST CASE EXECUTED : 3</t>
+  </si>
+  <si>
+    <t>TOTAL PASSED : 3</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 639 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 522 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 563 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 334 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 205 sec</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="84" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -148,8 +354,403 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -171,6 +772,21 @@
         <fgColor indexed="45"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -184,7 +800,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -209,6 +825,243 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="80" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,6 +1334,1052 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>147996</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>147996</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -800,16 +2699,16 @@
   <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="115.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="22.6640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="115.33203125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.88671875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.77734375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.21875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="9" max="14" bestFit="true" customWidth="true" width="2.109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -869,49 +2768,49 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <v>203.994</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="0">
         <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="F8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I8" s="0">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0">
+        <v>0</v>
+      </c>
+      <c r="L8" s="0">
+        <v>0</v>
+      </c>
+      <c r="M8" s="0">
+        <v>0</v>
+      </c>
+      <c r="N8" s="0">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s" s="0">
         <v>10</v>
       </c>
     </row>
@@ -926,16 +2825,16 @@
   <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="29.5546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="103.88671875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.88671875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.77734375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.21875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="9" max="14" bestFit="true" customWidth="true" width="2.109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -995,660 +2894,660 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <v>6.3E-2</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="F8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I8" s="0">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0">
+        <v>0</v>
+      </c>
+      <c r="L8" s="0">
+        <v>0</v>
+      </c>
+      <c r="M8" s="0">
+        <v>0</v>
+      </c>
+      <c r="N8" s="0">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0">
         <v>0.05</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="F9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I9" s="0">
+        <v>0</v>
+      </c>
+      <c r="J9" s="0">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0">
+        <v>0</v>
+      </c>
+      <c r="L9" s="0">
+        <v>0</v>
+      </c>
+      <c r="M9" s="0">
+        <v>0</v>
+      </c>
+      <c r="N9" s="0">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="F10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I10" s="0">
+        <v>0</v>
+      </c>
+      <c r="J10" s="0">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0">
+        <v>0</v>
+      </c>
+      <c r="L10" s="0">
+        <v>0</v>
+      </c>
+      <c r="M10" s="0">
+        <v>0</v>
+      </c>
+      <c r="N10" s="0">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0">
         <v>2.7E-2</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="F11" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I11" s="0">
+        <v>0</v>
+      </c>
+      <c r="J11" s="0">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0">
+        <v>0</v>
+      </c>
+      <c r="L11" s="0">
+        <v>0</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0</v>
+      </c>
+      <c r="N11" s="0">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="0">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="F12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I12" s="0">
+        <v>0</v>
+      </c>
+      <c r="J12" s="0">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0">
+        <v>0</v>
+      </c>
+      <c r="L12" s="0">
+        <v>0</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0</v>
+      </c>
+      <c r="N12" s="0">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="0">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="F13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I13" s="0">
+        <v>0</v>
+      </c>
+      <c r="J13" s="0">
+        <v>0</v>
+      </c>
+      <c r="K13" s="0">
+        <v>0</v>
+      </c>
+      <c r="L13" s="0">
+        <v>0</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0</v>
+      </c>
+      <c r="N13" s="0">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="0">
         <v>19.225000000000001</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="F14" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I14" s="0">
+        <v>0</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0">
+        <v>0</v>
+      </c>
+      <c r="L14" s="0">
+        <v>0</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0</v>
+      </c>
+      <c r="N14" s="0">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="0">
         <v>27.119</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
+      <c r="F15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I15" s="0">
+        <v>0</v>
+      </c>
+      <c r="J15" s="0">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0">
+        <v>0</v>
+      </c>
+      <c r="L15" s="0">
+        <v>0</v>
+      </c>
+      <c r="M15" s="0">
+        <v>0</v>
+      </c>
+      <c r="N15" s="0">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="0">
         <v>37.308999999999997</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
+      <c r="F16" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I16" s="0">
+        <v>0</v>
+      </c>
+      <c r="J16" s="0">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0">
+        <v>0</v>
+      </c>
+      <c r="L16" s="0">
+        <v>0</v>
+      </c>
+      <c r="M16" s="0">
+        <v>0</v>
+      </c>
+      <c r="N16" s="0">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="0">
         <v>22.631</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" t="s">
-        <v>10</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
+      <c r="F17" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I17" s="0">
+        <v>0</v>
+      </c>
+      <c r="J17" s="0">
+        <v>0</v>
+      </c>
+      <c r="K17" s="0">
+        <v>0</v>
+      </c>
+      <c r="L17" s="0">
+        <v>0</v>
+      </c>
+      <c r="M17" s="0">
+        <v>0</v>
+      </c>
+      <c r="N17" s="0">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="0">
         <v>35.372</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
+      <c r="F18" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I18" s="0">
+        <v>0</v>
+      </c>
+      <c r="J18" s="0">
+        <v>0</v>
+      </c>
+      <c r="K18" s="0">
+        <v>0</v>
+      </c>
+      <c r="L18" s="0">
+        <v>0</v>
+      </c>
+      <c r="M18" s="0">
+        <v>0</v>
+      </c>
+      <c r="N18" s="0">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="0">
         <v>23.553000000000001</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" t="s">
-        <v>10</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
+      <c r="F19" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I19" s="0">
+        <v>0</v>
+      </c>
+      <c r="J19" s="0">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0">
+        <v>0</v>
+      </c>
+      <c r="L19" s="0">
+        <v>0</v>
+      </c>
+      <c r="M19" s="0">
+        <v>0</v>
+      </c>
+      <c r="N19" s="0">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="0">
         <v>36.389000000000003</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="F20" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" t="s">
-        <v>10</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="F20" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I20" s="0">
+        <v>0</v>
+      </c>
+      <c r="J20" s="0">
+        <v>0</v>
+      </c>
+      <c r="K20" s="0">
+        <v>0</v>
+      </c>
+      <c r="L20" s="0">
+        <v>0</v>
+      </c>
+      <c r="M20" s="0">
+        <v>0</v>
+      </c>
+      <c r="N20" s="0">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="0">
         <v>33.140999999999998</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E21" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="F21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" t="s">
-        <v>10</v>
-      </c>
-      <c r="H21" t="s">
-        <v>10</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="F21" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I21" s="0">
+        <v>0</v>
+      </c>
+      <c r="J21" s="0">
+        <v>0</v>
+      </c>
+      <c r="K21" s="0">
+        <v>0</v>
+      </c>
+      <c r="L21" s="0">
+        <v>0</v>
+      </c>
+      <c r="M21" s="0">
+        <v>0</v>
+      </c>
+      <c r="N21" s="0">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s" s="0">
         <v>10</v>
       </c>
     </row>
@@ -1656,4 +3555,4208 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="29.60546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="134.33203125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="53">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="53">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="53">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="53">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="53">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="53">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="53">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="20">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s" s="20">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s" s="20">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s" s="20">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s" s="20">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s" s="20">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>67.128</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s" s="21">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>0.027</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s" s="24">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>0.015</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s" s="27">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>0.013</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>0.015</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s" s="33">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>0.022</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s" s="36">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O13" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>0.021</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s" s="39">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>0.014</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s" s="42">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O15" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>0.017</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s" s="45">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O16" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>44.703</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s" s="48">
+        <v>17</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O17" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>46.014</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s" s="51">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O18" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O32"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="30.51171875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="116.98828125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="132">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="132">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="132">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="132">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="132">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="132">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="132">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s" s="54">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s" s="54">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s" s="54">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s" s="54">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s" s="54">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s" s="54">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s" s="54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>92.589</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s" s="56">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>81.525</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s" s="58">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>127.788</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s" s="62">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>87.649</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s" s="65">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>104.663</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s" s="67">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>87.587</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s" s="70">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O13" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>113.523</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s" s="74">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>178.716</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s" s="77">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O15" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>160.639</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s" s="80">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O16" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>144.527</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s" s="83">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O17" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>164.133</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s" s="86">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O18" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>165.956</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s" s="89">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O19" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>263.332</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s" s="92">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O20" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>104.071</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E21" t="s" s="95">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O21" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>192.012</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E22" t="s" s="98">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O22" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>124.835</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s" s="100">
+        <v>17</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O23" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>125.18</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s" s="103">
+        <v>17</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O24" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>124.943</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E25" t="s" s="106">
+        <v>17</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O25" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>127.933</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s" s="110">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O26" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>90.196</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s" s="112">
+        <v>17</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O27" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>115.625</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s" s="115">
+        <v>17</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O28" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>107.018</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E29" t="s" s="118">
+        <v>17</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O29" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>107.58</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s" s="122">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O30" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>153.24</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E31" t="s" s="124">
+        <v>17</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O31" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>178.369</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s" s="128">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O32" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="30.51171875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="116.98828125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="175">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="175">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="175">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="175">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="175">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="175">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="175">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s" s="133">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s" s="133">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s" s="133">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s" s="133">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s" s="133">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s" s="133">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s" s="133">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>173.712</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s" s="134">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>180.384</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s" s="138">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>119.005</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s" s="140">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>213.346</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s" s="144">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>51.006</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s" s="147">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>127.035</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s" s="152">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O13" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>134.258</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s" s="155">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>143.428</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s" s="159">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O15" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>44.432</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s" s="162">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O16" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>173.005</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s" s="165">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O17" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>114.52</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s" s="167">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O18" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>114.164</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s" s="170">
+        <v>17</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O19" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>134.324</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s" s="173">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O20" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="30.51171875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="116.98828125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="209">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="209">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="209">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="209">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="209">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="209">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="209">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s" s="176">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s" s="176">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s" s="176">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s" s="176">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s" s="176">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s" s="176">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s" s="176">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>133.087</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s" s="177">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>103.284</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s" s="181">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>127.033</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s" s="184">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>226.337</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s" s="187">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>261.428</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s" s="189">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>114.33</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s" s="192">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O13" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>223.629</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s" s="192">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>152.391</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s" s="201">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O15" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>236.772</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s" s="204">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O16" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>221.996</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s" s="208">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O17" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="30.51171875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="116.98828125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="228">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="228">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="228">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="228">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="228">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="228">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="228">
+        <v>93</v>
+      </c>
+      <c r="B7" t="s" s="210">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s" s="210">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s" s="210">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s" s="210">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s" s="210">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s" s="210">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s" s="210">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>259.401</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s" s="211">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>274.631</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s" s="214">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>248.007</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s" s="217">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>267.256</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s" s="220">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>215.709</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s" s="223">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>210.085</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s" s="223">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O13" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>213.244</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s" s="223">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>111.213</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s" s="226">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O15" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>167.544</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s" s="226">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O16" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>243.544</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s" s="226">
+        <v>17</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O17" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:O10"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="19.44140625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="116.98828125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="232">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="232">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="232">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="232">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="232">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="232">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="232">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s" s="229">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s" s="229">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s" s="229">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s" s="229">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s" s="229">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s" s="229">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s" s="229">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>124.679</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s" s="230">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>223.71</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s" s="230">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>215.255</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s" s="230">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="29.60546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="116.98828125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="242">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="242">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="242">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="242">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="242">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="242">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="242">
+        <v>96</v>
+      </c>
+      <c r="B7" t="s" s="233">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s" s="233">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s" s="233">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s" s="233">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s" s="233">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s" s="233">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s" s="233">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>105.003</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s" s="234">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>208.349</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s" s="234">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>20.952</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s" s="235">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>51.161</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s" s="238">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>205.84</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s" s="240">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>